--- a/Team-Data/2013-14/1-20-2013-14.xlsx
+++ b/Team-Data/2013-14/1-20-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>0.525</v>
+        <v>0.513</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J2" t="n">
         <v>82.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
@@ -709,10 +776,10 @@
         <v>31.8</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="V2" t="n">
         <v>15.2</v>
@@ -721,25 +788,25 @@
         <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y2" t="n">
         <v>4.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.2</v>
+        <v>101.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -775,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
@@ -805,10 +872,10 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -921,25 +988,25 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
         <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
         <v>23</v>
@@ -954,19 +1021,19 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>21</v>
@@ -981,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -990,13 +1057,13 @@
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -1025,64 +1092,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.436</v>
+        <v>0.421</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
         <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="N4" t="n">
         <v>0.371</v>
       </c>
       <c r="O4" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P4" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0.76</v>
       </c>
       <c r="R4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U4" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
         <v>4.1</v>
@@ -1091,28 +1158,28 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1130,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="AM4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN4" t="n">
         <v>8</v>
@@ -1139,28 +1206,28 @@
         <v>6</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1178,7 +1245,7 @@
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.419</v>
+        <v>0.405</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,40 +1292,40 @@
         <v>35</v>
       </c>
       <c r="J5" t="n">
-        <v>81.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.343</v>
       </c>
       <c r="O5" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P5" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S5" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T5" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V5" t="n">
         <v>12.8</v>
@@ -1270,19 +1337,19 @@
         <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA5" t="n">
         <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1294,7 +1361,7 @@
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>13</v>
@@ -1303,7 +1370,7 @@
         <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,40 +1382,40 @@
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP5" t="n">
         <v>9</v>
       </c>
-      <c r="AP5" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>23</v>
       </c>
       <c r="AU5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -1389,34 +1456,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.425</v>
+        <v>0.426</v>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M6" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N6" t="n">
         <v>0.334</v>
@@ -1428,31 +1495,31 @@
         <v>23.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>45.3</v>
+        <v>45.1</v>
       </c>
       <c r="U6" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V6" t="n">
         <v>16.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z6" t="n">
         <v>19.3</v>
@@ -1461,31 +1528,31 @@
         <v>21.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1500,13 +1567,13 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1524,7 +1591,7 @@
         <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="H7" t="n">
         <v>49</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
         <v>0.427</v>
@@ -1601,22 +1668,22 @@
         <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.362</v>
+        <v>0.366</v>
       </c>
       <c r="O7" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R7" t="n">
         <v>12.1</v>
       </c>
       <c r="S7" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T7" t="n">
         <v>44.5</v>
@@ -1628,19 +1695,19 @@
         <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AB7" t="n">
         <v>96.7</v>
@@ -1649,22 +1716,22 @@
         <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>23</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
@@ -1673,19 +1740,19 @@
         <v>28</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
@@ -1694,7 +1761,7 @@
         <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
@@ -1703,19 +1770,19 @@
         <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AY7" t="n">
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.581</v>
+        <v>0.571</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1777,58 +1844,58 @@
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="O8" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q8" t="n">
         <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U8" t="n">
         <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W8" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X8" t="n">
         <v>4.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AB8" t="n">
         <v>104</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1840,10 +1907,10 @@
         <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AP8" t="n">
         <v>27</v>
@@ -1882,7 +1949,7 @@
         <v>29</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>5</v>
@@ -1897,13 +1964,13 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
         <v>30</v>
@@ -2046,7 +2113,7 @@
         <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
@@ -2070,19 +2137,19 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
         <v>26</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
         <v>11</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.415</v>
+        <v>0.425</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,40 +2202,40 @@
         <v>38.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.307</v>
+        <v>0.31</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P10" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.662</v>
+        <v>0.66</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>44.7</v>
+        <v>45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
         <v>15.5</v>
@@ -2180,31 +2247,31 @@
         <v>5.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB10" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF10" t="n">
         <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
         <v>16</v>
@@ -2222,7 +2289,7 @@
         <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV10" t="n">
         <v>24</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>23</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2270,7 +2337,7 @@
         <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2299,55 +2366,55 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
         <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.605</v>
+        <v>0.619</v>
       </c>
       <c r="H11" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J11" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L11" t="n">
         <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.386</v>
+        <v>0.387</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R11" t="n">
         <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="T11" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="U11" t="n">
         <v>23</v>
@@ -2359,7 +2426,7 @@
         <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
         <v>4.7</v>
@@ -2371,10 +2438,10 @@
         <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.6</v>
+        <v>103.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2392,13 +2459,13 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL11" t="n">
         <v>2</v>
@@ -2410,10 +2477,10 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2481,61 +2548,61 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.651</v>
+        <v>0.643</v>
       </c>
       <c r="H12" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O12" t="n">
         <v>21.9</v>
       </c>
       <c r="P12" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="U12" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W12" t="n">
         <v>7.4</v>
@@ -2544,19 +2611,19 @@
         <v>6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.6</v>
+        <v>105.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2607,16 +2674,16 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,13 +2692,13 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2663,55 +2730,55 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.825</v>
+        <v>0.821</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J13" t="n">
-        <v>80</v>
+        <v>79.7</v>
       </c>
       <c r="K13" t="n">
         <v>0.457</v>
       </c>
       <c r="L13" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
         <v>19.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O13" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P13" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
         <v>0.791</v>
       </c>
       <c r="R13" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="U13" t="n">
         <v>20.8</v>
@@ -2732,16 +2799,16 @@
         <v>19.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>9.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2756,7 +2823,7 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
@@ -2765,31 +2832,31 @@
         <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>21</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
       </c>
       <c r="AP13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ13" t="n">
         <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
         <v>2</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
         <v>17</v>
@@ -2798,7 +2865,7 @@
         <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2807,7 +2874,7 @@
         <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.674</v>
+        <v>0.667</v>
       </c>
       <c r="H14" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J14" t="n">
-        <v>82.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L14" t="n">
         <v>8.1</v>
       </c>
       <c r="M14" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O14" t="n">
         <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.733</v>
       </c>
       <c r="R14" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T14" t="n">
         <v>43.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
@@ -2911,22 +2978,22 @@
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.8</v>
+        <v>105.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2941,13 +3008,13 @@
         <v>13</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
@@ -2962,22 +3029,22 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>8</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3027,19 +3094,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.381</v>
+        <v>0.39</v>
       </c>
       <c r="H15" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I15" t="n">
         <v>36.9</v>
@@ -3048,7 +3115,7 @@
         <v>83.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L15" t="n">
         <v>9.199999999999999</v>
@@ -3057,37 +3124,37 @@
         <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O15" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U15" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V15" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y15" t="n">
         <v>4.7</v>
@@ -3105,19 +3172,19 @@
         <v>-5.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF15" t="n">
         <v>21</v>
       </c>
-      <c r="AF15" t="n">
-        <v>23</v>
-      </c>
       <c r="AG15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>19</v>
@@ -3144,25 +3211,25 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX15" t="n">
         <v>6</v>
@@ -3174,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3209,67 +3276,67 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0.513</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="K16" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="P16" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.751</v>
+        <v>0.748</v>
       </c>
       <c r="R16" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T16" t="n">
         <v>43.1</v>
       </c>
       <c r="U16" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W16" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="X16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y16" t="n">
         <v>5.6</v>
@@ -3278,34 +3345,34 @@
         <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB16" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI16" t="n">
         <v>15</v>
       </c>
-      <c r="AI16" t="n">
-        <v>17</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>13</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>26</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,7 +3411,7 @@
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>20</v>
@@ -3356,13 +3423,13 @@
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.707</v>
+        <v>0.725</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,28 +3476,28 @@
         <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.506</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.376</v>
+        <v>0.373</v>
       </c>
       <c r="O17" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P17" t="n">
         <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R17" t="n">
         <v>7.1</v>
@@ -3442,10 +3509,10 @@
         <v>36.6</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
         <v>9.199999999999999</v>
@@ -3457,19 +3524,19 @@
         <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.2</v>
+        <v>104</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM17" t="n">
         <v>14</v>
@@ -3502,13 +3569,13 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,10 +3587,10 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
@@ -3535,16 +3602,16 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3675,22 +3742,22 @@
         <v>30</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR18" t="n">
         <v>13</v>
@@ -3708,7 +3775,7 @@
         <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3848,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3860,10 +3927,10 @@
         <v>15</v>
       </c>
       <c r="AM19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3887,7 +3954,7 @@
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
         <v>2</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
         <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4</v>
+        <v>0.385</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J20" t="n">
-        <v>85.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K20" t="n">
         <v>0.454</v>
@@ -3964,10 +4031,10 @@
         <v>6.2</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="O20" t="n">
         <v>17.4</v>
@@ -3976,28 +4043,28 @@
         <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R20" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W20" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
         <v>6.3</v>
@@ -4009,28 +4076,28 @@
         <v>20.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.8</v>
+        <v>101</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH20" t="n">
         <v>11</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
         <v>6</v>
@@ -4045,25 +4112,25 @@
         <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4075,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="J21" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="L21" t="n">
         <v>8.4</v>
       </c>
       <c r="M21" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O21" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.76</v>
+        <v>0.766</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U21" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W21" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X21" t="n">
         <v>4.4</v>
@@ -4185,25 +4252,25 @@
         <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4.2</v>
+        <v>-3.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4212,10 +4279,10 @@
         <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
@@ -4230,28 +4297,28 @@
         <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW21" t="n">
         <v>12</v>
@@ -4269,10 +4336,10 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -4379,25 +4446,25 @@
         <v>7.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH22" t="n">
         <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -4427,7 +4494,7 @@
         <v>1</v>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="n">
         <v>16</v>
@@ -4439,7 +4506,7 @@
         <v>11</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
@@ -4448,10 +4515,10 @@
         <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,7 +4640,7 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>23</v>
@@ -4585,7 +4652,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM23" t="n">
         <v>15</v>
@@ -4594,10 +4661,10 @@
         <v>25</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ23" t="n">
         <v>19</v>
@@ -4612,7 +4679,7 @@
         <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4621,13 +4688,13 @@
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -4665,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
         <v>13</v>
       </c>
       <c r="F24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>0.317</v>
+        <v>0.325</v>
       </c>
       <c r="H24" t="n">
         <v>48.9</v>
       </c>
       <c r="I24" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J24" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.441</v>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.315</v>
+        <v>0.317</v>
       </c>
       <c r="O24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.707</v>
+        <v>0.708</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T24" t="n">
         <v>44.9</v>
       </c>
       <c r="U24" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V24" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="W24" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC24" t="n">
         <v>-8.699999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,13 +4822,13 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI24" t="n">
         <v>5</v>
       </c>
-      <c r="AI24" t="n">
-        <v>4</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
         <v>19</v>
@@ -4785,16 +4852,16 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS24" t="n">
         <v>9</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4809,7 +4876,7 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -4943,7 +5010,7 @@
         <v>10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
         <v>12</v>
@@ -4955,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
         <v>16</v>
@@ -4967,7 +5034,7 @@
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4985,13 +5052,13 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5029,64 +5096,64 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.756</v>
+        <v>0.775</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J26" t="n">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
         <v>10.2</v>
       </c>
       <c r="M26" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.395</v>
+        <v>0.397</v>
       </c>
       <c r="O26" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>33.6</v>
+        <v>33.9</v>
       </c>
       <c r="T26" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="U26" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
@@ -5095,25 +5162,25 @@
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB26" t="n">
         <v>109.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
         <v>3</v>
@@ -5125,7 +5192,7 @@
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>9</v>
@@ -5140,7 +5207,7 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5155,7 +5222,7 @@
         <v>6</v>
       </c>
       <c r="AT26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU26" t="n">
         <v>3</v>
@@ -5167,13 +5234,13 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5304,13 +5371,13 @@
         <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
@@ -5319,19 +5386,19 @@
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
         <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
         <v>17</v>
@@ -5340,10 +5407,10 @@
         <v>13</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>14</v>
@@ -5355,7 +5422,7 @@
         <v>25</v>
       </c>
       <c r="AZ27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5538,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,13 +5571,13 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5531,7 +5598,7 @@
         <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>14</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>0.513</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
         <v>0.436</v>
       </c>
       <c r="L29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M29" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="N29" t="n">
         <v>0.361</v>
       </c>
       <c r="O29" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S29" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
         <v>20.2</v>
@@ -5632,7 +5699,7 @@
         <v>14.4</v>
       </c>
       <c r="W29" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
@@ -5644,49 +5711,49 @@
         <v>22.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="AB29" t="n">
         <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
       </c>
       <c r="AL29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM29" t="n">
         <v>12</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>11</v>
       </c>
       <c r="AN29" t="n">
         <v>14</v>
       </c>
       <c r="AO29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
         <v>10</v>
@@ -5695,22 +5762,22 @@
         <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>19</v>
@@ -5719,7 +5786,7 @@
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
         <v>26</v>
@@ -5868,31 +5935,31 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
         <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="H31" t="n">
         <v>48.8</v>
@@ -5960,34 +6027,34 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M31" t="n">
         <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.73</v>
+        <v>0.727</v>
       </c>
       <c r="R31" t="n">
         <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="T31" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U31" t="n">
         <v>23.1</v>
@@ -5996,37 +6063,37 @@
         <v>15.2</v>
       </c>
       <c r="W31" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
         <v>3.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>6</v>
@@ -6038,7 +6105,7 @@
         <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6047,22 +6114,22 @@
         <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6071,28 +6138,28 @@
         <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AY31" t="n">
         <v>5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-20-2013-14</t>
+          <t>2014-01-20</t>
         </is>
       </c>
     </row>
